--- a/data/trans_orig/IP38E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Clase-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17173</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>25779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45628</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41332</t>
+          <t>42322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52665</t>
+          <t>52782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85908</t>
+          <t>85140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97060</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29159</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>36790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52558</t>
+          <t>52564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77084</t>
+          <t>76655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87756</t>
+          <t>87815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>55847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54713</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64953</t>
+          <t>64937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103425</t>
+          <t>104496</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118399</t>
+          <t>118419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154708</t>
+          <t>155358</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173156</t>
+          <t>173265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>196854</t>
+          <t>198394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213829</t>
+          <t>214296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>358486</t>
+          <t>357833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383711</t>
+          <t>383742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38079</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>63957</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP38E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP38E_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>35518</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>823</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14865</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12612</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15360</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13664</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15232</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13598</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10316</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15237</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>67,71%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15451</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12811</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16047</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>79,83%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>41</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>28464</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>24833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5062</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15360</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15360</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15360</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15232</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15232</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15232</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9908</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7194</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7547</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10972</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9908</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9908</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9908</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7194</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7194</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7194</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43987</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37461</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47208</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>43696</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39944</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>45545</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>39542</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52782</t>
+          <t>41249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>92684</t>
+          <t>83528</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85140</t>
+          <t>77493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>87833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6094</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12620</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6680</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>50081</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>50081</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>50081</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>46624</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>46624</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>46624</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>92426</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>92426</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>92426</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45965</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41495</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48658</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33854</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29465</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36790</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>85,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49706</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45114</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>83560</t>
+          <t>81549</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76655</t>
+          <t>75095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87815</t>
+          <t>85923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2543</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9706</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5845</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2909</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10234</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51201</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51201</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51201</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>39699</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>39699</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>39699</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>95116</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95116</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95116</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>57403</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>51606</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>61512</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>51001</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>44591</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>86,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60956</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55213</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64937</t>
+          <t>56948</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>67,54%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>86,04%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>109292</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>100504</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>116197</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>88,26%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>79,95%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>94,02%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>111957</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>104496</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>118419</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -2548,107 +2548,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13868</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13663</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8817</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20073</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>32,46%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>22369</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>15464</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>31157</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>11,74%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>21772</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>15310</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>29233</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>64664</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>64664</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>64664</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69064</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69064</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69064</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>133729</t>
+          <t>131661</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133729</t>
+          <t>131661</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>133729</t>
+          <t>131661</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>191758</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>182780</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>198552</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>85,95%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>165575</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>155358</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>173265</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>207064</t>
+          <t>164048</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198394</t>
+          <t>155517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214296</t>
+          <t>171856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>372638</t>
+          <t>355806</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>357833</t>
+          <t>343582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383742</t>
+          <t>365587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20903</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14109</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29881</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>19582</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>37489</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>25544</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>46447</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>212661</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>212661</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>212661</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>192847</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>192847</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>192847</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>228943</t>
+          <t>189592</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228943</t>
+          <t>189592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228943</t>
+          <t>189592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>421790</t>
+          <t>402253</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>421790</t>
+          <t>402253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>421790</t>
+          <t>402253</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
